--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/CABO - 15_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/CABO - 15_01.xlsx
@@ -482,7 +482,11 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -503,7 +507,11 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -524,7 +532,11 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -545,7 +557,11 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -591,7 +607,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -612,7 +632,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -633,7 +657,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -654,7 +682,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -675,7 +707,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -696,7 +732,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -717,7 +757,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -738,7 +782,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -759,7 +807,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -780,7 +832,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -801,7 +857,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -822,7 +882,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -843,7 +907,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -864,7 +932,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -885,7 +957,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -906,7 +982,11 @@
           <t>13</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -927,7 +1007,11 @@
           <t>23</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -948,7 +1032,11 @@
           <t>11</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -961,7 +1049,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CABO ACELERADOR KCABOS FAZER250 2016 121186</t>
+          <t>CABO ACELERADOR LAQUILA  FAZER250 2016 121186</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -969,7 +1057,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -982,7 +1074,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CABO ACELERADOR B KCABOS FAZER150 1211795</t>
+          <t>CABO ACELERADOR B LAQUILA  FAZER150 1211795</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -990,7 +1082,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1011,7 +1107,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1032,7 +1132,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1053,7 +1157,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1074,7 +1182,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1095,7 +1207,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1116,7 +1232,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1137,7 +1257,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1158,7 +1282,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1171,7 +1299,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CABO ACELERADOR CONTROLFLEX XTZ125 2003 A 2008 9020830176</t>
+          <t>CABO ACELERADOR VINI XTZ125 2003 A 2008 9020830176</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1179,7 +1307,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1200,7 +1332,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1221,7 +1357,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1242,7 +1382,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1263,7 +1407,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1284,7 +1432,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1305,7 +1457,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1326,7 +1482,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1347,7 +1507,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1368,7 +1532,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1381,7 +1549,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CABO ACELERADOR A K-CABOS NXR160 1104245</t>
+          <t>CABO ACELERADOR A LAQUILA  NXR160 1104245</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1389,7 +1557,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1402,7 +1574,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CABO ACELERADOR B K-CABOS NXR160 1104246</t>
+          <t>CABO ACELERADOR B LAQUILA  NXR160 1104246</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1410,7 +1582,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1431,7 +1607,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1452,7 +1632,11 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1473,7 +1657,11 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1494,7 +1682,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1515,7 +1707,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1536,7 +1732,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1557,7 +1757,11 @@
           <t>8</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1578,7 +1782,11 @@
           <t>8</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1591,7 +1799,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>CABO EMBREAGEM K-CABOS XRE190 1104491</t>
+          <t>CABO EMBREAGEM LAQUILA  XRE190 1104491</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1599,7 +1807,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1612,7 +1824,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CABO ACELERADOR B K-CABOS XRE190</t>
+          <t>CABO ACELERADOR B LAQUILA  XRE190</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1620,7 +1832,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1641,7 +1857,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1662,7 +1882,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1683,7 +1907,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1704,7 +1932,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1725,7 +1957,11 @@
           <t>11</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1738,7 +1974,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CABO EMBREAGEM K-CABOS FAZER250 2018 121197</t>
+          <t>CABO EMBREAGEM LAQUILA  FAZER250 2018 121197</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -1746,7 +1982,11 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1767,7 +2007,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -1788,7 +2032,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -1801,7 +2049,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CABO EMBREAMGEM K-CABOS LANDER 250/ XTZ250 2020  1212260</t>
+          <t>CABO EMBREAMGEM LAQUILA  LANDER 250/ XTZ250 2020  1212260</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -1809,7 +2057,11 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -1830,7 +2082,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -1851,7 +2107,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -1872,7 +2132,11 @@
           <t>8</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -1893,7 +2157,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -1914,7 +2182,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -1935,7 +2207,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -1956,7 +2232,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -1977,7 +2257,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -1990,7 +2274,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>CABO VELOCIMETRO K-CABOS XY-50Q 1280026</t>
+          <t>CABO VELOCIMETRO LAQUILA  XY-50Q 1280026</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -1998,7 +2282,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -2019,7 +2307,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -2040,7 +2332,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -2061,7 +2357,11 @@
           <t>11</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -2082,7 +2382,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -2095,7 +2399,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>CABO FREIO DIANTEIRO K-CABOS CG125 2002 A 2008 1103409</t>
+          <t>CABO FREIO DIANTEIRO LAQUILA  CG125 2002 A 2008 1103409</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2103,7 +2407,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -2124,7 +2432,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -2145,7 +2457,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -2166,7 +2482,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -2187,7 +2507,11 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -2208,7 +2532,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -2229,7 +2557,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr"/>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -2250,7 +2582,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -2271,7 +2607,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr"/>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -2292,7 +2632,11 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -2313,7 +2657,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -2334,7 +2682,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -2355,7 +2707,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -2376,7 +2732,11 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -2397,7 +2757,11 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -2418,7 +2782,11 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -2439,7 +2807,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -2460,7 +2832,11 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -2473,7 +2849,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>CABO FREIO AUXILIAR K-CABOS PCX150 2014 1103832</t>
+          <t>CABO FREIO AUXILIAR LAQUILA  PCX150 2014 1103832</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -2481,7 +2857,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -2494,7 +2874,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>CABO FREIO TRASEIRO K-CABOS PCX150 2014 1103830</t>
+          <t>CABO FREIO TRASEIRO LAQUILA  PCX150 2014 1103830</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -2502,7 +2882,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -2523,7 +2907,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -2544,7 +2932,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -2557,7 +2949,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t xml:space="preserve"> CABO EMBREAGEM K-CABOS YBR125 121187</t>
+          <t xml:space="preserve"> CABO EMBREAGEM LAQUILA  YBR125 121187</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -2565,7 +2957,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -2586,7 +2982,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -2607,7 +3007,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -2628,7 +3032,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr"/>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -2649,7 +3057,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -2670,7 +3082,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr"/>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -2691,7 +3107,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -2712,7 +3132,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -2733,7 +3157,11 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr"/>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -2754,7 +3182,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr"/>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -2775,7 +3207,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr"/>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -2796,7 +3232,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -2817,7 +3257,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr"/>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -2838,7 +3282,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr"/>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -2859,7 +3307,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr"/>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -2880,7 +3332,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr"/>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -2901,7 +3357,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr"/>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -2922,7 +3382,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr"/>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -2943,7 +3407,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr"/>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -2964,7 +3432,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr"/>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -2985,7 +3457,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr"/>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -3006,7 +3482,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr"/>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -3019,7 +3499,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>CABO VELOCIMETRO K-CABOS POP100 1100607</t>
+          <t>CABO VELOCIMETRO LAQUILA  POP100 1100607</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -3027,7 +3507,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr"/>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -3048,7 +3532,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr"/>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -3069,7 +3557,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr"/>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -3090,7 +3582,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr"/>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -3111,7 +3607,11 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr"/>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -3124,7 +3624,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>CABO ACELERADOR A K-CABOS XTZ150 CROSSER 121164</t>
+          <t>CABO ACELERADOR A LAQUILA  XTZ150 CROSSER 121164</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3132,7 +3632,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr"/>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -3153,7 +3657,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr"/>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -3174,7 +3682,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -3195,7 +3707,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr"/>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -3208,7 +3724,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>CABO ACELERADOR A/B K-CABOS XTZ150 CROSSER 1210526</t>
+          <t>CABO ACELERADOR A/B LAQUILA  XTZ150 CROSSER 1210526</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -3216,7 +3732,11 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr"/>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -3237,7 +3757,11 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr"/>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -3258,7 +3782,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr"/>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -3279,7 +3807,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr"/>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -3300,7 +3832,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr"/>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -3321,7 +3857,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr"/>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -3342,7 +3882,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr"/>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -3363,7 +3907,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr"/>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -3384,7 +3932,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr"/>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -3405,7 +3957,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -3426,7 +3982,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr"/>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -3447,7 +4007,11 @@
           <t>18</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr"/>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -3468,7 +4032,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr"/>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -3489,7 +4057,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr"/>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -3510,7 +4082,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr"/>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -3531,7 +4107,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr"/>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -3544,7 +4124,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>CABO EMBREAGEM K-CABOS XRE300 2013 1102569</t>
+          <t>CABO EMBREAGEM LAQUILA  XRE300 2013 1102569</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -3552,7 +4132,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr"/>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -3565,7 +4149,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>CABO EMBREAGEM SOLIDEX XRE300</t>
+          <t>CABO EMBREAGEM SOLIDEZ XRE300</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -3573,7 +4157,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr"/>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -3594,7 +4182,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr"/>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -3615,7 +4207,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr"/>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -3636,7 +4232,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr"/>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -3649,7 +4249,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>CABO FREIO TRASEIRO K-CABOS BURGMAN225 2011 1250206</t>
+          <t>CABO FREIO TRASEIRO LAQUILA  BURGMAN225 2011 1250206</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -3674,7 +4274,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>CABO FREIO TRASEIRO K-CABOS BURGMAN125 2005 A 2010 1250112</t>
+          <t>CABO FREIO TRASEIRO LAQUILA  BURGMAN125 2005 A 2010 1250112</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -3707,7 +4307,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr"/>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -3728,7 +4332,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr"/>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -3741,7 +4349,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>CABO EMBREAGEM K-CABOS FAZER250 2006 A 2014 1210188</t>
+          <t>CABO EMBREAGEM LAQUILA  FAZER250 2006 A 2014 1210188</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -3749,7 +4357,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr"/>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -3762,7 +4374,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>CABO EMBREAGEM K-CABOS FAZER250 2016 121188</t>
+          <t>CABO EMBREAGEM LAQUILA  FAZER250 2016 121188</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -3770,7 +4382,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr"/>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -3791,7 +4407,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr"/>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -3812,7 +4432,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr"/>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -3833,7 +4457,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr"/>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -3854,7 +4482,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr"/>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -3867,7 +4499,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>CABO VELOCIMETRO K-CABOS YBR125 2002 1210288</t>
+          <t>CABO VELOCIMETRO LAQUILA  YBR125 2002 1210288</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -3875,7 +4507,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr"/>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -3896,7 +4532,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr"/>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -3917,7 +4557,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E166" t="inlineStr"/>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -3938,7 +4582,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr"/>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -3959,7 +4607,11 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E168" t="inlineStr"/>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -3980,7 +4632,11 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E169" t="inlineStr"/>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -4001,7 +4657,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr"/>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -4022,7 +4682,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E171" t="inlineStr"/>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -4043,7 +4707,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E172" t="inlineStr"/>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -4064,7 +4732,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E173" t="inlineStr"/>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -4085,7 +4757,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E174" t="inlineStr"/>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -4106,7 +4782,11 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E175" t="inlineStr"/>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -4127,7 +4807,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E176" t="inlineStr"/>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -4148,7 +4832,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E177" t="inlineStr"/>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -4169,7 +4857,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E178" t="inlineStr"/>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -4182,7 +4874,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>CABO VELOCIMETRO K-CABOS CG125 2000 A 2008/ NXR125/ 150 KS 110678</t>
+          <t>CABO VELOCIMETRO LAQUILA  CG125 2000 A 2008/ NXR125/ 150 KS 110678</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -4190,7 +4882,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E179" t="inlineStr"/>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -4211,7 +4907,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E180" t="inlineStr"/>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -4232,7 +4932,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E181" t="inlineStr"/>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -4253,7 +4957,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E182" t="inlineStr"/>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -4274,7 +4982,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E183" t="inlineStr"/>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -4295,7 +5007,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E184" t="inlineStr"/>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -4316,7 +5032,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E185" t="inlineStr"/>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -4337,7 +5057,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E186" t="inlineStr"/>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -4358,7 +5082,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E187" t="inlineStr"/>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -4371,7 +5099,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>CABO EMBREAGEM K-CABOS XRE190 1104491</t>
+          <t>CABO EMBREAGEM LAQUILA  XRE190 1104491</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -4379,7 +5107,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E188" t="inlineStr"/>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -4392,7 +5124,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>CABO EMBREAGEM K-CABOS CB300R 1102676</t>
+          <t>CABO EMBREAGEM LAQUILA  CB300R 1102676</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -4400,7 +5132,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E189" t="inlineStr"/>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -4413,7 +5149,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>CABO EMBREAMGEM ABS K-CABOS CB300R 1102637</t>
+          <t>CABO EMBREAMGEM ABS LAQUILA  CB300R 1102637</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -4421,7 +5157,11 @@
           <t>13</t>
         </is>
       </c>
-      <c r="E190" t="inlineStr"/>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -4442,7 +5182,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E191" t="inlineStr"/>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -4463,7 +5207,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E192" t="inlineStr"/>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -4484,7 +5232,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E193" t="inlineStr"/>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -4505,7 +5257,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E194" t="inlineStr"/>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -4518,7 +5274,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>CABO EMBREAGEM K-CABOS CG160/ CG150 2014 A 2015 1103899</t>
+          <t>CABO EMBREAGEM LAQUILA  CG160/ CG150 2014 A 2015 1103899</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -4526,7 +5282,11 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E195" t="inlineStr"/>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -4547,7 +5307,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E196" t="inlineStr"/>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -4568,7 +5332,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E197" t="inlineStr"/>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -4589,7 +5357,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E198" t="inlineStr"/>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -4610,7 +5382,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E199" t="inlineStr"/>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -4631,7 +5407,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E200" t="inlineStr"/>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -4652,7 +5432,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E201" t="inlineStr"/>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -4673,7 +5457,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E202" t="inlineStr"/>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -4694,7 +5482,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E203" t="inlineStr"/>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -4715,7 +5507,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E204" t="inlineStr"/>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -4736,7 +5532,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E205" t="inlineStr"/>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -4757,7 +5557,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E206" t="inlineStr"/>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -4770,7 +5574,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>CABO ACELERADOR B K-CABOS FAZER150 1211795</t>
+          <t>CABO ACELERADOR B LAQUILA  FAZER150 1211795</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -4778,7 +5582,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E207" t="inlineStr"/>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -4799,7 +5607,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E208" t="inlineStr"/>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -4820,7 +5632,11 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E209" t="inlineStr"/>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -4841,7 +5657,11 @@
           <t>8</t>
         </is>
       </c>
-      <c r="E210" t="inlineStr"/>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -4862,7 +5682,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E211" t="inlineStr"/>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -4883,7 +5707,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E212" t="inlineStr"/>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -4904,7 +5732,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E213" t="inlineStr"/>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -4925,7 +5757,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E214" t="inlineStr"/>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -4946,7 +5782,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E215" t="inlineStr"/>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -4959,7 +5799,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>CABO ACELERADOR A K-CABOS PCX150 2016 A 2018 1101976</t>
+          <t>CABO ACELERADOR A LAQUILA  PCX150 2016 A 2018 1101976</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -4984,7 +5824,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>CABO ACELERADOR B K-CABOS PCX150 2016 A 2018 1101977</t>
+          <t>CABO ACELERADOR B LAQUILA  PCX150 2016 A 2018 1101977</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -5009,7 +5849,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>CABO ACELERADOR K-CABOS PCX150 2014 A 2015 1103831</t>
+          <t>CABO ACELERADOR LAQUILA  PCX150 2014 A 2015 1103831</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -5017,7 +5857,11 @@
           <t>11</t>
         </is>
       </c>
-      <c r="E218" t="inlineStr"/>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -5038,7 +5882,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E219" t="inlineStr"/>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -5059,7 +5907,11 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E220" t="inlineStr"/>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -5261,7 +6113,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>CABO VELOCIMETRO K-CABOS BIZ125 1100606</t>
+          <t>CABO VELOCIMETRO LAQUILA  BIZ125 1100606</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -5849,7 +6701,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>CABO ACELERADOR A K-CABOS XRE300 2009 A 2015 1103402</t>
+          <t>CABO ACELERADOR A LAQUILA  XRE300 2009 A 2015 1103402</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -5870,7 +6722,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>CABO ACELERADOR B K-CABOS XRE300 2009 A 2015 1103404</t>
+          <t>CABO ACELERADOR B LAQUILA  XRE300 2009 A 2015 1103404</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -5891,7 +6743,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>CABO ACELERADOR B K-CABOS XRE300 2016 A 2018 1105255</t>
+          <t>CABO ACELERADOR B LAQUILA  XRE300 2016 A 2018 1105255</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -5912,7 +6764,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>CABO ACELERADOR A K-CABOS XRE300 2019 1105256</t>
+          <t>CABO ACELERADOR A LAQUILA  XRE300 2019 1105256</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -5933,7 +6785,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>CABO ACELERADOR B K-CABOS XRE300 2019 1105257</t>
+          <t>CABO ACELERADOR B LAQUILA  XRE300 2019 1105257</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -6466,7 +7318,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E287" t="inlineStr"/>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -6487,7 +7343,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E288" t="inlineStr"/>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -6508,7 +7368,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E289" t="inlineStr"/>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -6529,7 +7393,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E290" t="inlineStr"/>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -6550,7 +7418,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E291" t="inlineStr"/>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -6571,7 +7443,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E292" t="inlineStr"/>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -6592,7 +7468,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E293" t="inlineStr"/>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -6613,7 +7493,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E294" t="inlineStr"/>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -6634,7 +7518,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E295" t="inlineStr"/>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -6655,7 +7543,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E296" t="inlineStr"/>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -6676,7 +7568,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E297" t="inlineStr"/>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -6697,7 +7593,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E298" t="inlineStr"/>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -6718,7 +7618,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E299" t="inlineStr"/>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -6739,7 +7643,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E300" t="inlineStr"/>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -6760,7 +7668,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E301" t="inlineStr"/>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -6781,7 +7693,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E302" t="inlineStr"/>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -6802,7 +7718,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E303" t="inlineStr"/>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -6823,7 +7743,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E304" t="inlineStr"/>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -6844,7 +7768,11 @@
           <t>11</t>
         </is>
       </c>
-      <c r="E305" t="inlineStr"/>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -6865,7 +7793,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E306" t="inlineStr"/>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -6878,7 +7810,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>CABO EMBREAGEM K-CABOS XTZ150 CROSSER 1210527</t>
+          <t>CABO EMBREAGEM LAQUILA  XTZ150 CROSSER 1210527</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -6886,7 +7818,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E307" t="inlineStr"/>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -6907,7 +7843,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E308" t="inlineStr"/>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -6928,7 +7868,11 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E309" t="inlineStr"/>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -6949,7 +7893,11 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E310" t="inlineStr"/>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -6970,7 +7918,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E311" t="inlineStr"/>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -6991,7 +7943,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E312" t="inlineStr"/>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -7012,7 +7968,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E313" t="inlineStr"/>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -7025,7 +7985,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>CABO VELOCIMETRO K-CABOS YES125/ KATANA 1250055</t>
+          <t>CABO VELOCIMETRO LAQUILA  YES125/ KATANA 1250055</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -7033,7 +7993,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E314" t="inlineStr"/>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -7046,7 +8010,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t xml:space="preserve">CABO ACELERADOR DUPLO CONTROLFLEX XTZ250 LANDER 2007 </t>
+          <t xml:space="preserve">CABO ACELERADOR DUPLO VINI XTZ250 LANDER 2007 </t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -7054,7 +8018,11 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E315" t="inlineStr"/>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -7075,7 +8043,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E316" t="inlineStr"/>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -7088,7 +8060,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>CABO VELOCIMETRO K-CABOS SUZUKI/ YES125 2011 1250209</t>
+          <t>CABO VELOCIMETRO LAQUILA  SUZUKI/ YES125 2011 1250209</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -7096,7 +8068,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E317" t="inlineStr"/>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -7117,7 +8093,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E318" t="inlineStr"/>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -7138,7 +8118,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E319" t="inlineStr"/>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -7159,7 +8143,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E320" t="inlineStr"/>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -7180,7 +8168,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E321" t="inlineStr"/>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -7201,7 +8193,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E322" t="inlineStr"/>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -7222,7 +8218,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E323" t="inlineStr"/>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -7243,7 +8243,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E324" t="inlineStr"/>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -7264,7 +8268,11 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E325" t="inlineStr"/>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -7285,7 +8293,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E326" t="inlineStr"/>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -7306,7 +8318,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E327" t="inlineStr"/>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -7327,7 +8343,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E328" t="inlineStr"/>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -7348,7 +8368,11 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E329" t="inlineStr"/>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -7369,7 +8393,11 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E330" t="inlineStr"/>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -7382,7 +8410,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>CABO ACELERADOR A K-CABOS XR250 1100596</t>
+          <t>CABO ACELERADOR A LAQUILA  XR250 1100596</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
@@ -7390,7 +8418,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E331" t="inlineStr"/>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -7403,7 +8435,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>CABO ACELERADOR B K-CABOS XR250 110597</t>
+          <t>CABO ACELERADOR B LAQUILA  XR250 110597</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -7411,7 +8443,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E332" t="inlineStr"/>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -7432,7 +8468,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E333" t="inlineStr"/>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -7453,7 +8493,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E334" t="inlineStr"/>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -7474,7 +8518,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E335" t="inlineStr"/>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -7495,7 +8543,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E336" t="inlineStr"/>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -7512,7 +8564,11 @@
         </is>
       </c>
       <c r="D337" t="inlineStr"/>
-      <c r="E337" t="inlineStr"/>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -7529,7 +8585,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E338" t="inlineStr"/>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/CABO - 15_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/CABO - 15_01.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E338"/>
+  <dimension ref="A1:D338"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,11 +452,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -482,11 +472,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -507,11 +492,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -532,11 +512,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -557,11 +532,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -582,11 +552,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,11 +572,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -632,11 +592,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -657,11 +612,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -682,11 +632,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -707,11 +652,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -732,11 +672,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -757,11 +692,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -782,11 +712,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -807,11 +732,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -832,11 +752,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -857,11 +772,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -882,11 +792,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -907,11 +812,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -932,11 +832,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -957,11 +852,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -982,11 +872,6 @@
           <t>13</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1007,11 +892,6 @@
           <t>23</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1032,11 +912,6 @@
           <t>11</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1057,11 +932,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1082,11 +952,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1107,11 +972,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1132,11 +992,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1157,11 +1012,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1182,11 +1032,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1207,11 +1052,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1232,11 +1072,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1257,11 +1092,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1282,11 +1112,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1307,11 +1132,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1332,11 +1152,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1357,11 +1172,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1382,11 +1192,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1407,11 +1212,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1432,11 +1232,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1457,11 +1252,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1482,11 +1272,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1507,11 +1292,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1532,11 +1312,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1557,11 +1332,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1582,11 +1352,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1607,11 +1372,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1632,11 +1392,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1657,11 +1412,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1682,11 +1432,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1707,11 +1452,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1732,11 +1472,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1757,11 +1492,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1782,11 +1512,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1807,11 +1532,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1832,11 +1552,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1857,11 +1572,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1882,11 +1592,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1907,11 +1612,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1932,11 +1632,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1957,11 +1652,6 @@
           <t>11</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1982,11 +1672,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -2007,11 +1692,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -2032,11 +1712,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -2057,11 +1732,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -2082,11 +1752,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -2107,11 +1772,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -2132,11 +1792,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -2157,11 +1812,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -2182,11 +1832,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -2207,11 +1852,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -2232,11 +1872,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -2257,11 +1892,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -2282,11 +1912,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -2307,11 +1932,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -2332,11 +1952,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -2357,11 +1972,6 @@
           <t>11</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -2382,11 +1992,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -2407,11 +2012,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -2432,11 +2032,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -2457,11 +2052,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -2482,11 +2072,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -2507,11 +2092,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -2532,11 +2112,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -2557,11 +2132,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -2582,11 +2152,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -2607,11 +2172,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -2632,11 +2192,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -2657,11 +2212,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -2682,11 +2232,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -2707,11 +2252,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -2732,11 +2272,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -2757,11 +2292,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -2782,11 +2312,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -2807,11 +2332,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -2832,11 +2352,6 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -2857,11 +2372,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -2882,11 +2392,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -2907,11 +2412,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -2932,11 +2432,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -2957,11 +2452,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -2982,11 +2472,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -3007,11 +2492,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -3032,11 +2512,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -3057,11 +2532,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -3082,11 +2552,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -3107,11 +2572,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -3132,11 +2592,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -3157,11 +2612,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -3182,11 +2632,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -3207,11 +2652,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -3232,11 +2672,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -3257,11 +2692,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -3282,11 +2712,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -3307,11 +2732,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -3332,11 +2752,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -3357,11 +2772,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -3382,11 +2792,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -3407,11 +2812,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -3432,11 +2832,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -3457,11 +2852,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -3482,11 +2872,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -3507,11 +2892,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -3532,11 +2912,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -3557,11 +2932,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -3582,11 +2952,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -3607,11 +2972,6 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -3632,11 +2992,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -3657,11 +3012,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -3682,11 +3032,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -3707,11 +3052,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -3732,11 +3072,6 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -3757,11 +3092,6 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -3782,11 +3112,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -3807,11 +3132,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -3832,11 +3152,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -3857,11 +3172,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -3882,11 +3192,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -3907,11 +3212,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -3932,11 +3232,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -3957,11 +3252,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -3982,11 +3272,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -4007,11 +3292,6 @@
           <t>18</t>
         </is>
       </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -4032,11 +3312,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -4057,11 +3332,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -4082,11 +3352,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -4107,11 +3372,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -4132,11 +3392,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -4157,11 +3412,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -4182,11 +3432,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -4207,11 +3452,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -4232,11 +3472,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -4257,11 +3492,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -4282,11 +3512,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -4307,11 +3532,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -4332,11 +3552,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -4357,11 +3572,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -4382,11 +3592,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -4407,11 +3612,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -4432,11 +3632,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -4457,11 +3652,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -4482,11 +3672,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -4507,11 +3692,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -4532,11 +3712,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -4557,11 +3732,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -4582,11 +3752,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -4607,11 +3772,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -4632,11 +3792,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -4657,11 +3812,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -4682,11 +3832,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -4707,11 +3852,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -4732,11 +3872,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -4757,11 +3892,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -4782,11 +3912,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -4807,11 +3932,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -4832,11 +3952,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -4857,11 +3972,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -4882,11 +3992,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -4907,11 +4012,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -4932,11 +4032,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -4957,11 +4052,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -4982,11 +4072,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -5007,11 +4092,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -5032,11 +4112,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -5057,11 +4132,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -5082,11 +4152,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -5107,11 +4172,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -5132,11 +4192,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -5157,11 +4212,6 @@
           <t>13</t>
         </is>
       </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -5182,11 +4232,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -5207,11 +4252,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -5232,11 +4272,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -5257,11 +4292,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -5282,11 +4312,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -5307,11 +4332,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -5332,11 +4352,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -5357,11 +4372,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -5382,11 +4392,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -5407,11 +4412,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -5432,11 +4432,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -5457,11 +4452,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -5482,11 +4472,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -5507,11 +4492,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -5532,11 +4512,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -5557,11 +4532,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -5582,11 +4552,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -5607,11 +4572,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -5632,11 +4592,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -5657,11 +4612,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -5682,11 +4632,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -5707,11 +4652,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -5732,11 +4672,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -5757,11 +4692,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -5782,11 +4712,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -5807,11 +4732,6 @@
           <t>12</t>
         </is>
       </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -5832,11 +4752,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -5857,11 +4772,6 @@
           <t>11</t>
         </is>
       </c>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -5882,11 +4792,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -5907,11 +4812,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -5932,7 +4832,6 @@
           <t>17</t>
         </is>
       </c>
-      <c r="E221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -5953,7 +4852,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -5974,7 +4872,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -5995,7 +4892,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -6016,7 +4912,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -6037,7 +4932,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -6058,7 +4952,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -6079,7 +4972,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -6100,7 +4992,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -6121,7 +5012,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -6142,7 +5032,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -6163,7 +5052,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -6184,7 +5072,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -6205,7 +5092,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -6226,7 +5112,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -6247,7 +5132,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -6268,7 +5152,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -6289,7 +5172,6 @@
           <t>15</t>
         </is>
       </c>
-      <c r="E238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -6310,7 +5192,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -6331,7 +5212,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -6352,7 +5232,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -6373,7 +5252,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -6394,7 +5272,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -6415,7 +5292,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -6436,7 +5312,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -6457,7 +5332,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -6478,7 +5352,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -6499,7 +5372,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -6520,7 +5392,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -6541,7 +5412,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -6562,7 +5432,6 @@
           <t>14</t>
         </is>
       </c>
-      <c r="E251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -6583,7 +5452,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -6604,7 +5472,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -6625,7 +5492,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -6646,7 +5512,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -6667,7 +5532,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -6688,7 +5552,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -6709,7 +5572,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -6730,7 +5592,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E259" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -6751,7 +5612,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E260" t="inlineStr"/>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -6772,7 +5632,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -6793,7 +5652,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E262" t="inlineStr"/>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -6814,7 +5672,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -6835,7 +5692,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E264" t="inlineStr"/>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -6856,7 +5712,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -6877,7 +5732,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E266" t="inlineStr"/>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -6898,7 +5752,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E267" t="inlineStr"/>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -6919,7 +5772,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -6940,7 +5792,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E269" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -6961,7 +5812,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E270" t="inlineStr"/>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -6982,7 +5832,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -7003,7 +5852,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E272" t="inlineStr"/>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -7024,7 +5872,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E273" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -7045,7 +5892,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E274" t="inlineStr"/>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -7066,7 +5912,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E275" t="inlineStr"/>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -7087,7 +5932,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E276" t="inlineStr"/>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -7108,7 +5952,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E277" t="inlineStr"/>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -7129,7 +5972,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E278" t="inlineStr"/>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -7150,7 +5992,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E279" t="inlineStr"/>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -7171,7 +6012,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -7192,7 +6032,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -7213,7 +6052,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -7234,7 +6072,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E283" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -7255,7 +6092,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E284" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -7276,7 +6112,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E285" t="inlineStr"/>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -7297,7 +6132,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E286" t="inlineStr"/>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -7318,11 +6152,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E287" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -7343,11 +6172,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E288" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -7368,11 +6192,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E289" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -7393,11 +6212,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E290" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -7418,11 +6232,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E291" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -7443,11 +6252,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E292" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -7468,11 +6272,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E293" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -7493,11 +6292,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E294" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -7518,11 +6312,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E295" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -7543,11 +6332,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E296" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -7568,11 +6352,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E297" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -7593,11 +6372,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E298" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -7618,11 +6392,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E299" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -7643,11 +6412,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E300" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -7668,11 +6432,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E301" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -7693,11 +6452,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E302" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -7718,11 +6472,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E303" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -7743,11 +6492,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E304" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -7768,11 +6512,6 @@
           <t>11</t>
         </is>
       </c>
-      <c r="E305" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -7793,11 +6532,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E306" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -7818,11 +6552,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E307" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -7843,11 +6572,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E308" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -7868,11 +6592,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E309" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -7893,11 +6612,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E310" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -7918,11 +6632,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E311" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -7943,11 +6652,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E312" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -7968,11 +6672,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E313" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -7993,11 +6692,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E314" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -8018,11 +6712,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E315" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -8043,11 +6732,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E316" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -8068,11 +6752,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E317" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -8093,11 +6772,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E318" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -8118,11 +6792,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E319" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -8143,11 +6812,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E320" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -8168,11 +6832,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E321" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -8193,11 +6852,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E322" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -8218,11 +6872,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E323" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -8243,11 +6892,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E324" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -8268,11 +6912,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E325" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -8293,11 +6932,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E326" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -8318,11 +6952,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E327" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
@@ -8343,11 +6972,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E328" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -8368,11 +6992,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E329" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -8393,11 +7012,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E330" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -8418,11 +7032,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E331" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -8443,11 +7052,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E332" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -8468,11 +7072,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E333" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -8493,11 +7092,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E334" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -8518,11 +7112,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E335" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -8543,11 +7132,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E336" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -8563,10 +7147,9 @@
           <t>CABO EMBREAGEM IRON CB300R 122922</t>
         </is>
       </c>
-      <c r="D337" t="inlineStr"/>
-      <c r="E337" t="inlineStr">
-        <is>
-          <t>20</t>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -8583,11 +7166,6 @@
       <c r="D338" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="E338" t="inlineStr">
-        <is>
-          <t>20</t>
         </is>
       </c>
     </row>
